--- a/notebooks/01_first_analysis/table_5_2_checklist_compliance.xlsx
+++ b/notebooks/01_first_analysis/table_5_2_checklist_compliance.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,14 +446,14 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Asistente Lectura Facilitada "Francisco Javier Alvarez Jimenez"</t>
+          <t>Asistente de lectura fácil “Antonio Gonzales Crespo”</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D2" t="n">
-        <v>100</v>
+        <v>93.333</v>
       </c>
     </row>
     <row r="3">
@@ -464,43 +464,43 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Placea</t>
+          <t>Asistente Lectura Facilitada "Francisco Javier Alvarez Jimenez"</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>90</v>
+        <v>86.667</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G2</t>
+          <t>G1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>GPT 5.4 Think</t>
+          <t>Placea</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="D4" t="n">
-        <v>83.333</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G2</t>
+          <t>G1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>deepseek-v3.2</t>
+          <t xml:space="preserve">Asistente de lectura fácil “Mark Jonathan Camacho Escatel”: </t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -518,14 +518,14 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Gemini 3.1 Pro</t>
+          <t>Claude Sonnet 4.6</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="D6" t="n">
-        <v>76.667</v>
+        <v>93.333</v>
       </c>
     </row>
     <row r="7">
@@ -536,25 +536,25 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Claude Sonnet 4.6</t>
+          <t>GPT 5.4 Think</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D7" t="n">
-        <v>73.333</v>
+        <v>93.333</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>G3</t>
+          <t>G2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FACILE</t>
+          <t>deepseek-v3.2</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -567,19 +567,19 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G3</t>
+          <t>G2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Modelo_Qwen3.5_9B</t>
+          <t>Gemini 3.1 Pro</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D9" t="n">
-        <v>93.333</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10">
@@ -590,31 +590,67 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SimpleText (ClearText)</t>
+          <t>FACILE</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="D10" t="n">
-        <v>83.333</v>
+        <v>93.333</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>G3</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>SimpleText (ClearText)</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>14</v>
+      </c>
+      <c r="D11" t="n">
+        <v>93.333</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>G3</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Modelo_Qwen3.5_9B</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>10</v>
+      </c>
+      <c r="D12" t="n">
+        <v>66.667</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Lectura Fácil [Referencia]</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="C13" t="n">
         <v>15</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D13" t="n">
         <v>100</v>
       </c>
     </row>
